--- a/data/MK_FRED_DATA_20260617.xlsx
+++ b/data/MK_FRED_DATA_20260617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8367,6 +8367,1455 @@
         <v>4.97</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>14</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>20260501</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>14</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>20260504</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>14</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>14</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>14</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>20260507</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>14</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>14</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>14</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>14</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>20260513</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>14</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>14</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>14</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>14</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>14</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>14</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>14</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>14</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>20260526</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>14</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>14</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>14</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>14</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>14</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>14</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>14</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>14</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>14</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>14</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>14</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>14</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>14</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>14</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>15</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>20260501</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>15</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>20260504</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>15</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>15</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>15</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>20260507</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>15</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>15</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>15</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>15</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>20260513</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>15</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>15</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>15</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>15</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>15</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>15</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>15</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>15</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>20260526</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>15</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>15</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>15</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>15</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>15</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>15</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>15</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>15</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>15</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>15</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>15</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>15</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>15</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>15</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>15</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>20260616</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MK_FRED_DATA_20260617.xlsx
+++ b/data/MK_FRED_DATA_20260617.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6184,25 +6184,25 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3.668</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3.667</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3.666</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="254">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3.665</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.664</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3.663</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="259">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.662</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.661</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.657</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.655</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.653</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.651</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.649</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.644</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="268">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.643</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="270">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.641</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.64</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="273">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3.639</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="275">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.638</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="277">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.637</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="279">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="281">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -6920,48 +6920,48 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1.24161826</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1.24199489</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1.24212012</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1.24224503</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1.2423696</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1.24249383</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1.24286658</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1.24299087</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1.24311517</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1.24323913</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>1.24336207</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1.2437299</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>1.24385186</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>1.24397313</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1.24409407</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1.24421537</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1.24470615</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1.24483166</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1.24495718</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1.24508236</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1.245459</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1.24558528</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1.24571087</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1.24583579</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>1.24596107</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1.24633797</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1.24646364</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1.24658829</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>1.2467126</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1.24683727</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1.24721652</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="314">
@@ -7647,80 +7647,80 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1.24734436</v>
+        <v>1.24683727</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>4.97</v>
+        <v>1.24721652</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>5.02</v>
+        <v>1.24734436</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>4.98</v>
+        <v>1.24747013</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="324">
@@ -7877,11 +7877,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="325">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="330">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>5.03</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4.98</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="336">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="337">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>4.95</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>4.97</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="345">
@@ -8360,80 +8360,80 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>1.91</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1.95</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1.96</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="355">
@@ -8590,11 +8590,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="356">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="358">
@@ -8659,11 +8659,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="360">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="361">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="362">
@@ -8751,11 +8751,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="363">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="364">
@@ -8797,11 +8797,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="365">
@@ -8820,11 +8820,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="376">
@@ -9073,80 +9073,80 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="386">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="394">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="398">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="404">
@@ -9717,11 +9717,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="405">
@@ -9740,11 +9740,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="406">
@@ -9763,11 +9763,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="407">
@@ -9786,11 +9786,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="408">
@@ -9809,10 +9809,79 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>15</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>15</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>15</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
           <t>20260616</t>
         </is>
       </c>
-      <c r="E408" t="n">
+      <c r="E411" t="n">
         <v>2.29</v>
       </c>
     </row>
